--- a/ShelfMind-RPA/downloads/gvdRuta.xlsx
+++ b/ShelfMind-RPA/downloads/gvdRuta.xlsx
@@ -34,12 +34,162 @@
   <si>
     <t xml:space="preserve"> </t>
   </si>
+  <si>
+    <t>VENDEDOR 20</t>
+  </si>
+  <si>
+    <t>20-JOAQUIN PASSAPONTI</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>SUPERVISOR HUGO</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0/1</t>
+  </si>
+  <si>
+    <t>VENDEDOR 21</t>
+  </si>
+  <si>
+    <t>21-FERREYRA MAURICIO EMANUEL</t>
+  </si>
+  <si>
+    <t>10- DOMINGO</t>
+  </si>
+  <si>
+    <t>10-MARCHE FERNANDO</t>
+  </si>
+  <si>
+    <t>0/33</t>
+  </si>
+  <si>
+    <t>11- DOMINGO</t>
+  </si>
+  <si>
+    <t>11-SOLANO MARINA</t>
+  </si>
+  <si>
+    <t>SUPERVISOR ARIEL</t>
+  </si>
+  <si>
+    <t>0/2</t>
+  </si>
+  <si>
+    <t>12- DOMINGO</t>
+  </si>
+  <si>
+    <t>12-MERCADO RAFAEL</t>
+  </si>
+  <si>
+    <t>0/20</t>
+  </si>
+  <si>
+    <t>13- DOMINGO</t>
+  </si>
+  <si>
+    <t>13-REYNOSO ENZO PAT</t>
+  </si>
+  <si>
+    <t>0/12</t>
+  </si>
+  <si>
+    <t>14- DOMINGO</t>
+  </si>
+  <si>
+    <t>14-SOLIA WALTER</t>
+  </si>
+  <si>
+    <t>0/25</t>
+  </si>
+  <si>
+    <t>15- DOMINGO</t>
+  </si>
+  <si>
+    <t>15-GUARINO GABRIELA</t>
+  </si>
+  <si>
+    <t>0/60</t>
+  </si>
+  <si>
+    <t>16- DOMINGO</t>
+  </si>
+  <si>
+    <t>16-SANCHEZ DARIO</t>
+  </si>
+  <si>
+    <t>17- DOMINGO</t>
+  </si>
+  <si>
+    <t>17-RUGGER SEBASTIAN</t>
+  </si>
+  <si>
+    <t>0/58</t>
+  </si>
+  <si>
+    <t>18- DOMINGO</t>
+  </si>
+  <si>
+    <t>18-CESAR ALLENDE</t>
+  </si>
+  <si>
+    <t>19- DOMINGO</t>
+  </si>
+  <si>
+    <t>19-JOEL CABRERA</t>
+  </si>
+  <si>
+    <t>23 - DOMINGO</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>4- DOMINGO</t>
+  </si>
+  <si>
+    <t>04-GOMEZ MARCELO</t>
+  </si>
+  <si>
+    <t>0/52</t>
+  </si>
+  <si>
+    <t>6- DOMINGO</t>
+  </si>
+  <si>
+    <t>06-FRAILE BIBIANA</t>
+  </si>
+  <si>
+    <t>7- DOMINGO</t>
+  </si>
+  <si>
+    <t>07-MUÑOZ ESTEBAN</t>
+  </si>
+  <si>
+    <t>0/19</t>
+  </si>
+  <si>
+    <t>9- DOMINGO</t>
+  </si>
+  <si>
+    <t>09-RUMIN GERMAN</t>
+  </si>
+  <si>
+    <t>0/4</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -52,8 +202,13 @@
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -63,6 +218,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,10 +253,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -372,12 +544,12 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <cols>
-    <col min="1" max="1" width="4.29" customWidth="1"/>
-    <col min="2" max="2" width="13.14" customWidth="1"/>
+    <col min="1" max="1" width="4.43" customWidth="1"/>
+    <col min="2" max="2" width="13.29" customWidth="1"/>
     <col min="3" max="3" width="4.71" customWidth="1"/>
-    <col min="4" max="4" width="5.57" customWidth="1"/>
+    <col min="4" max="4" width="32.29" customWidth="1"/>
     <col min="5" max="5" width="5.29" customWidth="1"/>
-    <col min="6" max="6" width="7.14" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="12.29" customWidth="1"/>
     <col min="8" max="8" width="12.29" customWidth="1"/>
     <col min="9" max="9" width="2.86" customWidth="1"/>
@@ -432,11 +604,723 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" ht="13.5" customHeight="1">
+      <c r="A2" s="2">
+        <v>20</v>
+      </c>
+      <c t="s" r="B2" s="3">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c t="s" r="D2" s="3">
+        <v>9</v>
+      </c>
+      <c t="s" r="E2" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F2" s="3">
+        <v>11</v>
+      </c>
+      <c t="s" r="G2" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H2" s="3">
+        <v>13</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1</v>
+      </c>
+      <c r="M2" s="2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="13.5" customHeight="1">
+      <c r="A3" s="2">
+        <v>21</v>
+      </c>
+      <c t="s" r="B3" s="3">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c t="s" r="D3" s="3">
+        <v>15</v>
+      </c>
+      <c t="s" r="E3" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F3" s="3">
+        <v>11</v>
+      </c>
+      <c t="s" r="G3" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H3" s="3">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="13.5" customHeight="1">
+      <c r="A4" s="2">
+        <v>107</v>
+      </c>
+      <c t="s" r="B4" s="3">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c t="s" r="D4" s="3">
+        <v>17</v>
+      </c>
+      <c t="s" r="E4" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F4" s="3">
+        <v>11</v>
+      </c>
+      <c t="s" r="G4" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H4" s="3">
+        <v>18</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>33</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="13.5" customHeight="1">
+      <c r="A5" s="2">
+        <v>117</v>
+      </c>
+      <c t="s" r="B5" s="3">
+        <v>19</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c t="s" r="D5" s="3">
+        <v>20</v>
+      </c>
+      <c t="s" r="E5" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F5" s="3">
+        <v>21</v>
+      </c>
+      <c t="s" r="G5" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H5" s="3">
+        <v>22</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>2</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="13.5" customHeight="1">
+      <c r="A6" s="2">
+        <v>127</v>
+      </c>
+      <c t="s" r="B6" s="3">
+        <v>23</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c t="s" r="D6" s="3">
+        <v>24</v>
+      </c>
+      <c t="s" r="E6" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F6" s="3">
+        <v>11</v>
+      </c>
+      <c t="s" r="G6" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H6" s="3">
+        <v>25</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>20</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="13.5" customHeight="1">
+      <c r="A7" s="2">
+        <v>137</v>
+      </c>
+      <c t="s" r="B7" s="3">
+        <v>26</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c t="s" r="D7" s="3">
+        <v>27</v>
+      </c>
+      <c t="s" r="E7" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F7" s="3">
+        <v>21</v>
+      </c>
+      <c t="s" r="G7" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H7" s="3">
+        <v>28</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>12</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="13.5" customHeight="1">
+      <c r="A8" s="2">
+        <v>147</v>
+      </c>
+      <c t="s" r="B8" s="3">
+        <v>29</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c t="s" r="D8" s="3">
+        <v>30</v>
+      </c>
+      <c t="s" r="E8" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F8" s="3">
+        <v>11</v>
+      </c>
+      <c t="s" r="G8" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H8" s="3">
+        <v>31</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>25</v>
+      </c>
+      <c r="M8" s="2">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="13.5" customHeight="1">
+      <c r="A9" s="2">
+        <v>157</v>
+      </c>
+      <c t="s" r="B9" s="3">
+        <v>32</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c t="s" r="D9" s="3">
+        <v>33</v>
+      </c>
+      <c t="s" r="E9" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F9" s="3">
+        <v>21</v>
+      </c>
+      <c t="s" r="G9" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H9" s="3">
+        <v>34</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2">
+        <v>60</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="13.5" customHeight="1">
+      <c r="A10" s="2">
+        <v>167</v>
+      </c>
+      <c t="s" r="B10" s="3">
+        <v>35</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c t="s" r="D10" s="3">
+        <v>36</v>
+      </c>
+      <c t="s" r="E10" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F10" s="3">
+        <v>11</v>
+      </c>
+      <c t="s" r="G10" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H10" s="3">
+        <v>13</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="13.5" customHeight="1">
+      <c r="A11" s="2">
+        <v>177</v>
+      </c>
+      <c t="s" r="B11" s="3">
+        <v>37</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c t="s" r="D11" s="3">
+        <v>38</v>
+      </c>
+      <c t="s" r="E11" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F11" s="3">
+        <v>21</v>
+      </c>
+      <c t="s" r="G11" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H11" s="3">
+        <v>39</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>58</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="13.5" customHeight="1">
+      <c r="A12" s="2">
+        <v>187</v>
+      </c>
+      <c t="s" r="B12" s="3">
+        <v>40</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c t="s" r="D12" s="3">
+        <v>41</v>
+      </c>
+      <c t="s" r="E12" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F12" s="3">
+        <v>21</v>
+      </c>
+      <c t="s" r="G12" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H12" s="3">
+        <v>39</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>58</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="13.5" customHeight="1">
+      <c r="A13" s="2">
+        <v>197</v>
+      </c>
+      <c t="s" r="B13" s="3">
+        <v>42</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c t="s" r="D13" s="3">
+        <v>43</v>
+      </c>
+      <c t="s" r="E13" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F13" s="3">
+        <v>21</v>
+      </c>
+      <c t="s" r="G13" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H13" s="3">
+        <v>13</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="13.5" customHeight="1">
+      <c r="A14" s="2">
+        <v>237</v>
+      </c>
+      <c t="s" r="B14" s="3">
+        <v>44</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c t="s" r="D14" s="3">
+        <v>21</v>
+      </c>
+      <c t="s" r="E14" s="3">
+        <v>45</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c t="s" r="G14" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H14" s="3">
+        <v>13</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="13.5" customHeight="1">
+      <c r="A15" s="2">
+        <v>4007</v>
+      </c>
+      <c t="s" r="B15" s="3">
+        <v>46</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c t="s" r="D15" s="3">
+        <v>47</v>
+      </c>
+      <c t="s" r="E15" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F15" s="3">
+        <v>11</v>
+      </c>
+      <c t="s" r="G15" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H15" s="3">
+        <v>48</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2">
+        <v>52</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="13.5" customHeight="1">
+      <c r="A16" s="2">
+        <v>6007</v>
+      </c>
+      <c t="s" r="B16" s="3">
+        <v>49</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c t="s" r="D16" s="3">
+        <v>50</v>
+      </c>
+      <c t="s" r="E16" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F16" s="3">
+        <v>21</v>
+      </c>
+      <c t="s" r="G16" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H16" s="3">
+        <v>13</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="13.5" customHeight="1">
+      <c r="A17" s="2">
+        <v>7007</v>
+      </c>
+      <c t="s" r="B17" s="3">
+        <v>51</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c t="s" r="D17" s="3">
+        <v>52</v>
+      </c>
+      <c t="s" r="E17" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F17" s="3">
+        <v>11</v>
+      </c>
+      <c t="s" r="G17" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H17" s="3">
+        <v>53</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2">
+        <v>19</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="13.5" customHeight="1">
+      <c r="A18" s="2">
+        <v>9007</v>
+      </c>
+      <c t="s" r="B18" s="3">
+        <v>54</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c t="s" r="D18" s="3">
+        <v>55</v>
+      </c>
+      <c t="s" r="E18" s="3">
+        <v>10</v>
+      </c>
+      <c t="s" r="F18" s="3">
+        <v>21</v>
+      </c>
+      <c t="s" r="G18" s="5">
+        <v>12</v>
+      </c>
+      <c t="s" r="H18" s="3">
+        <v>56</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2">
+        <v>4</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:N1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:N18" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>